--- a/results_scenario_3/tables/table_fmf_scenario_3.xlsx
+++ b/results_scenario_3/tables/table_fmf_scenario_3.xlsx
@@ -479,37 +479,37 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30407.6 ± 13.2</t>
+          <t>50718.2 ± 16.2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>25311.8 ± 21.3</t>
+          <t>42181.1 ± 36.8</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>118.0 ± 4.3</t>
+          <t>202.2 ± 3.1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>11.0 ± 1.3</t>
+          <t>18.9 ± 1.2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>52.2 ± 0.6</t>
+          <t>93.0 ± 2.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>27.6 ± 2.7</t>
+          <t>47.0 ± 2.7</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1.4 ± 0.2</t>
+          <t>3.0 ± 0.7</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -534,37 +534,37 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>30782.8 ± 16.3</t>
+          <t>51388.1 ± 23.5</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>25587.4 ± 26.3</t>
+          <t>42664.8 ± 44.2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>120.8 ± 4.9</t>
+          <t>206.9 ± 3.4</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>11.8 ± 1.0</t>
+          <t>19.1 ± 1.2</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>53.4 ± 1.0</t>
+          <t>96.7 ± 2.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>28.4 ± 3.0</t>
+          <t>47.9 ± 2.6</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.4 ± 0.2</t>
+          <t>3.0 ± 0.7</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -589,37 +589,37 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31307.4 ± 27.8</t>
+          <t>52248.3 ± 28.2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>25986.8 ± 33.7</t>
+          <t>43346.2 ± 46.6</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>123.4 ± 5.0</t>
+          <t>210.2 ± 3.8</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>11.6 ± 1.0</t>
+          <t>19.3 ± 1.2</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>55.6 ± 0.8</t>
+          <t>98.9 ± 2.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>29.0 ± 3.2</t>
+          <t>48.7 ± 2.8</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.4 ± 0.2</t>
+          <t>3.0 ± 0.8</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -644,37 +644,37 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31814.6 ± 35.3</t>
+          <t>53108.1 ± 34.5</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>26386.6 ± 40.7</t>
+          <t>44026.2 ± 50.5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>124.8 ± 5.0</t>
+          <t>214.6 ± 4.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11.6 ± 0.6</t>
+          <t>19.9 ± 1.3</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>56.0 ± 1.2</t>
+          <t>101.5 ± 2.9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>29.8 ± 2.9</t>
+          <t>50.0 ± 2.6</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.6 ± 0.2</t>
+          <t>3.0 ± 0.8</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -699,37 +699,37 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>32335.4 ± 44.0</t>
+          <t>53985.3 ± 41.7</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>26800.8 ± 49.5</t>
+          <t>44731.8 ± 56.3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>125.8 ± 4.3</t>
+          <t>219.8 ± 4.9</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11.8 ± 0.5</t>
+          <t>20.9 ± 1.5</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>57.2 ± 1.6</t>
+          <t>105.4 ± 3.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>29.6 ± 2.6</t>
+          <t>50.5 ± 2.7</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.6 ± 0.2</t>
+          <t>3.0 ± 0.8</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -754,37 +754,37 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>32889.8 ± 43.6</t>
+          <t>54894.9 ± 46.1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>27208.2 ± 51.0</t>
+          <t>45377.8 ± 63.8</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>129.0 ± 4.5</t>
+          <t>223.1 ± 5.2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12.8 ± 0.5</t>
+          <t>21.4 ± 1.6</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>59.0 ± 2.2</t>
+          <t>107.2 ± 3.7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>30.2 ± 2.9</t>
+          <t>51.6 ± 2.9</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.6 ± 0.2</t>
+          <t>3.1 ± 0.8</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -809,37 +809,37 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>33468.8 ± 45.3</t>
+          <t>55816.3 ± 49.6</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>27640.2 ± 56.9</t>
+          <t>46048.1 ± 64.4</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>132.6 ± 4.3</t>
+          <t>226.8 ± 5.2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>13.4 ± 0.9</t>
+          <t>21.6 ± 1.9</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.0 ± 2.1</t>
+          <t>110.5 ± 3.4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>31.2 ± 2.5</t>
+          <t>52.0 ± 3.3</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.6 ± 0.2</t>
+          <t>3.1 ± 0.8</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -864,37 +864,37 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>34027.4 ± 45.1</t>
+          <t>56770.1 ± 60.9</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>28030.8 ± 53.5</t>
+          <t>46731.8 ± 73.6</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>136.4 ± 4.9</t>
+          <t>231.8 ± 5.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>14.2 ± 1.1</t>
+          <t>22.1 ± 1.9</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>62.6 ± 2.4</t>
+          <t>114.1 ± 3.3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>32.4 ± 2.4</t>
+          <t>52.9 ± 3.5</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.8 ± 0.3</t>
+          <t>3.2 ± 0.7</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -919,37 +919,37 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>34577.8 ± 49.8</t>
+          <t>57736.7 ± 59.1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>28420.0 ± 54.5</t>
+          <t>47428.5 ± 77.4</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>137.2 ± 6.0</t>
+          <t>235.8 ± 5.9</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>14.2 ± 1.1</t>
+          <t>23.1 ± 2.0</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>63.0 ± 3.0</t>
+          <t>115.3 ± 3.2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>32.8 ± 2.5</t>
+          <t>54.5 ± 3.4</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.8 ± 0.3</t>
+          <t>3.4 ± 0.7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -974,37 +974,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>35136.8 ± 58.5</t>
+          <t>58682.2 ± 67.2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>28810.4 ± 58.1</t>
+          <t>48099.3 ± 82.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>140.0 ± 6.5</t>
+          <t>240.8 ± 6.1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>14.6 ± 1.4</t>
+          <t>23.8 ± 2.1</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>65.4 ± 2.9</t>
+          <t>118.4 ± 3.2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>32.6 ± 2.9</t>
+          <t>55.9 ± 3.6</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.0 ± 0.4</t>
+          <t>3.5 ± 0.7</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1029,37 +1029,37 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>35612.4 ± 55.9</t>
+          <t>59494.3 ± 74.5</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>29139.6 ± 58.0</t>
+          <t>48640.2 ± 89.5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>142.4 ± 6.7</t>
+          <t>243.7 ± 5.8</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>14.6 ± 1.6</t>
+          <t>24.3 ± 1.9</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>67.8 ± 3.1</t>
+          <t>121.1 ± 3.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>32.6 ± 3.4</t>
+          <t>55.8 ± 3.5</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.0 ± 0.4</t>
+          <t>3.6 ± 0.8</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1084,37 +1084,37 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>36053.0 ± 50.7</t>
+          <t>60260.9 ± 77.1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>29446.0 ± 57.1</t>
+          <t>49166.1 ± 90.7</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>145.8 ± 7.8</t>
+          <t>246.4 ± 6.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>14.6 ± 1.6</t>
+          <t>23.9 ± 2.0</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>70.4 ± 4.1</t>
+          <t>124.2 ± 3.2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>33.4 ± 3.6</t>
+          <t>55.9 ± 3.4</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2.0 ± 0.4</t>
+          <t>3.5 ± 0.8</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1139,37 +1139,37 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>36500.6 ± 49.6</t>
+          <t>61008.1 ± 77.2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>29732.8 ± 57.6</t>
+          <t>49652.8 ± 90.8</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>146.8 ± 6.9</t>
+          <t>250.3 ± 5.8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>14.6 ± 1.6</t>
+          <t>24.9 ± 1.8</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>71.2 ± 4.2</t>
+          <t>126.6 ± 3.3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>33.8 ± 3.0</t>
+          <t>56.4 ± 3.3</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2.0 ± 0.5</t>
+          <t>3.5 ± 0.8</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1194,37 +1194,37 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>36951.2 ± 46.8</t>
+          <t>61741.3 ± 82.7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>30024.6 ± 54.1</t>
+          <t>50114.6 ± 99.5</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>147.0 ± 6.5</t>
+          <t>254.6 ± 6.2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>14.4 ± 1.8</t>
+          <t>25.3 ± 1.7</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>72.6 ± 3.7</t>
+          <t>130.1 ± 3.4</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>33.0 ± 2.9</t>
+          <t>56.7 ± 3.3</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2.0 ± 0.5</t>
+          <t>3.7 ± 0.7</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1249,37 +1249,37 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>37412.2 ± 45.6</t>
+          <t>62480.8 ± 81.0</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>30305.4 ± 59.0</t>
+          <t>50573.5 ± 93.5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>148.0 ± 6.8</t>
+          <t>257.6 ± 6.2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>15.0 ± 1.5</t>
+          <t>25.7 ± 1.8</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>74.0 ± 4.1</t>
+          <t>132.6 ± 3.8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>32.4 ± 2.6</t>
+          <t>56.9 ± 3.1</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.8 ± 0.5</t>
+          <t>3.7 ± 0.7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1304,37 +1304,37 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>37863.8 ± 47.1</t>
+          <t>63228.6 ± 84.3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>30578.6 ± 55.2</t>
+          <t>51043.1 ± 96.7</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>148.8 ± 6.8</t>
+          <t>260.7 ± 6.2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>14.6 ± 1.5</t>
+          <t>26.3 ± 1.8</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>74.8 ± 4.2</t>
+          <t>134.3 ± 3.3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>33.0 ± 2.7</t>
+          <t>57.7 ± 3.3</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.8 ± 0.5</t>
+          <t>3.9 ± 0.6</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1359,37 +1359,37 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>38313.0 ± 51.8</t>
+          <t>63981.7 ± 82.5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>30845.8 ± 52.7</t>
+          <t>51493.3 ± 93.4</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>149.8 ± 6.2</t>
+          <t>264.5 ± 6.2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>14.6 ± 1.6</t>
+          <t>26.6 ± 1.8</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>76.4 ± 3.7</t>
+          <t>137.1 ± 3.6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>32.6 ± 2.5</t>
+          <t>58.4 ± 3.3</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.8 ± 0.5</t>
+          <t>4.0 ± 0.6</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1414,37 +1414,37 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>38764.0 ± 48.3</t>
+          <t>64743.2 ± 85.2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>31117.8 ± 50.8</t>
+          <t>51962.9 ± 95.1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>151.4 ± 6.6</t>
+          <t>269.9 ± 6.4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>14.8 ± 1.3</t>
+          <t>27.2 ± 2.0</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>77.4 ± 3.9</t>
+          <t>140.7 ± 3.8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>33.0 ± 3.1</t>
+          <t>59.5 ± 3.2</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.8 ± 0.5</t>
+          <t>4.0 ± 0.6</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1469,37 +1469,37 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>39236.6 ± 53.3</t>
+          <t>65510.7 ± 85.8</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>31400.8 ± 46.7</t>
+          <t>52419.5 ± 92.8</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>154.4 ± 6.4</t>
+          <t>272.9 ± 6.8</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>15.6 ± 1.0</t>
+          <t>27.4 ± 2.0</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>78.8 ± 3.9</t>
+          <t>142.7 ± 4.1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>33.8 ± 3.1</t>
+          <t>60.5 ± 3.2</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2.0 ± 0.4</t>
+          <t>3.9 ± 0.6</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1524,37 +1524,37 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>39680.4 ± 59.1</t>
+          <t>66267.8 ± 91.1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>31643.6 ± 56.0</t>
+          <t>52880.4 ± 97.6</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>154.6 ± 6.3</t>
+          <t>274.6 ± 6.9</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>15.4 ± 1.2</t>
+          <t>27.1 ± 2.0</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>79.4 ± 3.5</t>
+          <t>144.4 ± 4.1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>34.0 ± 3.4</t>
+          <t>60.8 ± 3.3</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.8 ± 0.5</t>
+          <t>4.0 ± 0.6</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1579,37 +1579,37 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>40105.8 ± 64.8</t>
+          <t>67013.8 ± 94.1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>31833.6 ± 54.7</t>
+          <t>53230.7 ± 94.3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>157.4 ± 7.3</t>
+          <t>276.6 ± 6.5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>15.4 ± 1.3</t>
+          <t>27.2 ± 2.0</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>81.2 ± 3.8</t>
+          <t>146.2 ± 3.8</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>35.0 ± 3.3</t>
+          <t>60.9 ± 3.4</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.8 ± 0.5</t>
+          <t>4.1 ± 0.5</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1634,37 +1634,37 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>40559.8 ± 61.5</t>
+          <t>67736.8 ± 95.6</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>32066.2 ± 54.6</t>
+          <t>53590.9 ± 95.1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>159.6 ± 7.7</t>
+          <t>280.3 ± 6.2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>15.6 ± 1.0</t>
+          <t>27.8 ± 2.0</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>83.4 ± 4.1</t>
+          <t>148.3 ± 3.7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>34.8 ± 3.2</t>
+          <t>61.5 ± 3.3</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.8 ± 0.5</t>
+          <t>4.5 ± 0.6</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1689,37 +1689,37 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>41002.0 ± 61.3</t>
+          <t>68470.4 ± 93.5</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>32295.4 ± 60.1</t>
+          <t>53964.2 ± 93.0</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>164.0 ± 7.0</t>
+          <t>283.1 ± 6.5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>15.8 ± 0.9</t>
+          <t>28.4 ± 2.1</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>87.0 ± 3.9</t>
+          <t>149.9 ± 3.9</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>35.6 ± 3.1</t>
+          <t>62.1 ± 3.3</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.6 ± 0.4</t>
+          <t>4.5 ± 0.6</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1744,37 +1744,37 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>41456.4 ± 68.1</t>
+          <t>69181.8 ± 96.9</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>32543.0 ± 61.9</t>
+          <t>54312.6 ± 92.8</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>165.6 ± 7.1</t>
+          <t>286.5 ± 6.4</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>15.8 ± 0.9</t>
+          <t>29.1 ± 2.2</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>88.2 ± 3.8</t>
+          <t>152.0 ± 4.3</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>36.2 ± 3.4</t>
+          <t>62.5 ± 3.1</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.6 ± 0.4</t>
+          <t>4.8 ± 0.6</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1799,37 +1799,37 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>41873.4 ± 72.5</t>
+          <t>69884.1 ± 96.5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>32772.8 ± 60.9</t>
+          <t>54665.6 ± 94.1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>168.2 ± 7.8</t>
+          <t>290.1 ± 5.8</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>16.6 ± 1.1</t>
+          <t>29.2 ± 2.3</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>89.0 ± 4.1</t>
+          <t>154.1 ± 4.0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>37.0 ± 3.4</t>
+          <t>63.8 ± 3.3</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1.8 ± 0.5</t>
+          <t>4.9 ± 0.7</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1854,37 +1854,37 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>42303.6 ± 78.7</t>
+          <t>70594.4 ± 100.5</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>32997.4 ± 60.4</t>
+          <t>55043.2 ± 97.5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>169.6 ± 8.1</t>
+          <t>292.7 ± 6.4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>17.0 ± 1.2</t>
+          <t>30.3 ± 2.1</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>90.0 ± 4.1</t>
+          <t>154.6 ± 4.5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>36.6 ± 3.1</t>
+          <t>64.9 ± 3.3</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2.2 ± 0.5</t>
+          <t>5.0 ± 0.6</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1909,37 +1909,37 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>42701.8 ± 80.6</t>
+          <t>71289.0 ± 102.5</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>33231.8 ± 66.4</t>
+          <t>55411.1 ± 99.5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>173.2 ± 8.1</t>
+          <t>295.4 ± 6.9</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>17.4 ± 1.4</t>
+          <t>30.2 ± 2.1</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>91.4 ± 4.0</t>
+          <t>156.3 ± 4.8</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>38.4 ± 3.1</t>
+          <t>66.0 ± 3.6</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2.2 ± 0.5</t>
+          <t>5.0 ± 0.7</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1964,37 +1964,37 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>43107.2 ± 84.0</t>
+          <t>71971.5 ± 104.7</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>33432.8 ± 71.1</t>
+          <t>55788.1 ± 104.0</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>175.6 ± 9.1</t>
+          <t>298.6 ± 6.7</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>17.4 ± 1.6</t>
+          <t>30.6 ± 2.0</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>93.0 ± 4.8</t>
+          <t>157.8 ± 4.6</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>39.4 ± 3.0</t>
+          <t>67.2 ± 3.7</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2.2 ± 0.6</t>
+          <t>5.2 ± 0.7</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2019,37 +2019,37 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>43470.8 ± 86.9</t>
+          <t>72631.9 ± 109.1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>33612.0 ± 82.6</t>
+          <t>56140.4 ± 105.2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>178.8 ± 9.5</t>
+          <t>300.9 ± 6.1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>18.0 ± 1.7</t>
+          <t>30.5 ± 2.0</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>94.8 ± 5.3</t>
+          <t>159.8 ± 4.8</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>39.8 ± 3.0</t>
+          <t>67.6 ± 3.5</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2.6 ± 0.5</t>
+          <t>5.2 ± 0.7</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2074,37 +2074,37 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>43865.2 ± 97.3</t>
+          <t>73275.9 ± 110.4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>33850.8 ± 85.7</t>
+          <t>56494.8 ± 107.5</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>180.4 ± 9.0</t>
+          <t>303.0 ± 5.9</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>18.4 ± 1.6</t>
+          <t>30.3 ± 2.0</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>96.2 ± 5.3</t>
+          <t>161.8 ± 4.8</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>39.6 ± 2.8</t>
+          <t>68.5 ± 3.5</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2.6 ± 0.5</t>
+          <t>5.2 ± 0.8</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2129,37 +2129,37 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>44268.8 ± 96.1</t>
+          <t>73899.4 ± 109.5</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>34097.2 ± 85.9</t>
+          <t>56839.2 ± 104.6</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>181.0 ± 8.3</t>
+          <t>306.7 ± 6.2</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>18.6 ± 1.6</t>
+          <t>30.9 ± 2.1</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>97.0 ± 5.1</t>
+          <t>164.1 ± 5.1</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>39.4 ± 2.5</t>
+          <t>69.3 ± 3.5</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2.6 ± 0.5</t>
+          <t>5.3 ± 0.8</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2184,37 +2184,37 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>44621.0 ± 91.7</t>
+          <t>74509.3 ± 108.8</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>34298.2 ± 86.1</t>
+          <t>57208.3 ± 103.2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>182.6 ± 8.8</t>
+          <t>307.6 ± 6.6</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>18.8 ± 1.8</t>
+          <t>30.9 ± 2.2</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>98.0 ± 5.4</t>
+          <t>164.7 ± 5.4</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>40.0 ± 2.3</t>
+          <t>69.8 ± 3.4</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2.4 ± 0.6</t>
+          <t>5.3 ± 0.8</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2239,37 +2239,37 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>45002.2 ± 96.8</t>
+          <t>75151.0 ± 110.2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>34542.8 ± 87.0</t>
+          <t>57602.4 ± 102.3</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>184.2 ± 8.0</t>
+          <t>308.9 ± 6.4</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>19.4 ± 2.1</t>
+          <t>31.6 ± 2.0</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>100.0 ± 5.3</t>
+          <t>167.2 ± 5.2</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>40.8 ± 2.0</t>
+          <t>71.1 ± 3.3</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2.4 ± 0.5</t>
+          <t>5.4 ± 0.7</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2294,37 +2294,37 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>45392.4 ± 98.2</t>
+          <t>75827.1 ± 115.4</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>34779.8 ± 90.4</t>
+          <t>58046.9 ± 108.8</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>185.0 ± 7.9</t>
+          <t>311.1 ± 6.5</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>19.2 ± 2.2</t>
+          <t>32.4 ± 2.1</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>100.8 ± 5.4</t>
+          <t>170.0 ± 5.3</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>43.0 ± 1.7</t>
+          <t>72.5 ± 3.6</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2.4 ± 0.5</t>
+          <t>5.5 ± 0.7</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2349,37 +2349,37 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>45799.8 ± 100.1</t>
+          <t>76523.0 ± 113.8</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>35063.8 ± 93.2</t>
+          <t>58521.7 ± 103.0</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>186.6 ± 6.3</t>
+          <t>312.9 ± 6.6</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>19.8 ± 2.1</t>
+          <t>32.8 ± 2.0</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>102.2 ± 4.9</t>
+          <t>172.9 ± 5.6</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>44.2 ± 1.4</t>
+          <t>73.5 ± 3.6</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2.2 ± 0.4</t>
+          <t>5.5 ± 0.8</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2404,37 +2404,37 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>46229.6 ± 110.2</t>
+          <t>77228.6 ± 115.6</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>35284.8 ± 101.4</t>
+          <t>58947.8 ± 104.9</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>187.6 ± 5.9</t>
+          <t>313.9 ± 6.9</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>20.2 ± 2.2</t>
+          <t>33.2 ± 1.9</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>104.2 ± 4.4</t>
+          <t>175.2 ± 5.5</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>45.0 ± 0.8</t>
+          <t>75.1 ± 3.6</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2.2 ± 0.4</t>
+          <t>5.5 ± 0.7</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2459,37 +2459,37 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>46633.6 ± 117.2</t>
+          <t>77917.3 ± 120.6</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>35534.0 ± 110.8</t>
+          <t>59378.4 ± 105.8</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>187.6 ± 6.2</t>
+          <t>314.4 ± 7.3</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>20.2 ± 2.3</t>
+          <t>33.5 ± 1.9</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>106.0 ± 4.4</t>
+          <t>177.8 ± 5.6</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>45.2 ± 0.9</t>
+          <t>75.5 ± 3.6</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2.2 ± 0.4</t>
+          <t>5.5 ± 0.8</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2514,37 +2514,37 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>47059.0 ± 105.6</t>
+          <t>78586.7 ± 131.0</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>35820.4 ± 102.0</t>
+          <t>59804.1 ± 110.5</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>189.0 ± 6.5</t>
+          <t>314.9 ± 7.6</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>20.4 ± 2.2</t>
+          <t>33.8 ± 1.6</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>108.0 ± 4.8</t>
+          <t>179.4 ± 5.6</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>45.8 ± 0.6</t>
+          <t>76.7 ± 3.5</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2.6 ± 0.5</t>
+          <t>5.8 ± 0.9</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2569,37 +2569,37 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>47167.2 ± 103.2</t>
+          <t>78770.9 ± 135.9</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>36010.6 ± 106.7</t>
+          <t>60111.9 ± 117.1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>187.6 ± 5.6</t>
+          <t>312.6 ± 7.5</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>20.8 ± 2.0</t>
+          <t>34.0 ± 1.8</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>109.2 ± 4.3</t>
+          <t>179.4 ± 5.7</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>45.0 ± 0.5</t>
+          <t>77.0 ± 3.5</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>3.0 ± 0.6</t>
+          <t>5.8 ± 0.9</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2624,37 +2624,37 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>47620.4 ± 103.0</t>
+          <t>79501.4 ± 139.7</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>36304.6 ± 112.0</t>
+          <t>60576.0 ± 123.8</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>187.6 ± 5.6</t>
+          <t>312.9 ± 7.1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>20.6 ± 1.7</t>
+          <t>34.2 ± 1.8</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>110.0 ± 4.8</t>
+          <t>181.7 ± 5.3</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>45.8 ± 0.5</t>
+          <t>78.0 ± 3.6</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>3.2 ± 0.7</t>
+          <t>6.1 ± 0.8</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2679,37 +2679,37 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>48003.0 ± 107.1</t>
+          <t>80200.9 ± 154.3</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>36500.2 ± 119.9</t>
+          <t>60942.6 ± 134.2</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>187.4 ± 6.2</t>
+          <t>313.8 ± 6.8</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>19.8 ± 1.7</t>
+          <t>34.7 ± 2.0</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>111.2 ± 4.8</t>
+          <t>183.2 ± 5.2</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>46.6 ± 0.5</t>
+          <t>79.0 ± 3.7</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>3.4 ± 0.7</t>
+          <t>6.0 ± 0.8</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2734,37 +2734,37 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>48401.2 ± 115.1</t>
+          <t>80816.7 ± 157.2</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>36701.4 ± 118.0</t>
+          <t>61263.8 ± 131.4</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>187.6 ± 5.9</t>
+          <t>313.8 ± 6.6</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>20.2 ± 1.8</t>
+          <t>35.1 ± 1.9</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>111.4 ± 4.7</t>
+          <t>184.2 ± 5.2</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>47.2 ± 1.1</t>
+          <t>80.0 ± 3.4</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>3.4 ± 0.7</t>
+          <t>6.0 ± 0.8</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2789,37 +2789,37 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>48765.6 ± 118.2</t>
+          <t>81338.3 ± 150.1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>36879.6 ± 121.2</t>
+          <t>61510.4 ± 126.2</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>187.4 ± 6.0</t>
+          <t>315.1 ± 6.6</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>20.2 ± 1.8</t>
+          <t>36.1 ± 2.2</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>112.2 ± 5.1</t>
+          <t>184.8 ± 5.3</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>47.2 ± 0.9</t>
+          <t>81.5 ± 3.3</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>3.8 ± 0.7</t>
+          <t>6.0 ± 0.8</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2844,37 +2844,37 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>49029.0 ± 128.1</t>
+          <t>81756.0 ± 149.3</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>36965.6 ± 132.4</t>
+          <t>61651.4 ± 127.6</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>188.2 ± 6.7</t>
+          <t>316.1 ± 6.5</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>20.2 ± 1.8</t>
+          <t>36.3 ± 2.4</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>113.2 ± 5.2</t>
+          <t>185.9 ± 5.4</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>48.0 ± 0.7</t>
+          <t>82.8 ± 3.2</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>3.8 ± 0.7</t>
+          <t>6.2 ± 0.8</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2899,37 +2899,37 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>49195.0 ± 130.7</t>
+          <t>82055.9 ± 158.2</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>36981.6 ± 139.9</t>
+          <t>61695.1 ± 131.1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>188.6 ± 6.5</t>
+          <t>315.8 ± 6.1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>20.2 ± 1.6</t>
+          <t>36.9 ± 2.4</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>114.0 ± 5.4</t>
+          <t>185.4 ± 5.3</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>48.6 ± 0.9</t>
+          <t>83.6 ± 3.3</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>4.0 ± 0.8</t>
+          <t>6.2 ± 0.8</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2954,37 +2954,37 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>49353.8 ± 128.7</t>
+          <t>82353.4 ± 155.6</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>36900.4 ± 140.5</t>
+          <t>61556.7 ± 128.7</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>188.0 ± 6.7</t>
+          <t>316.1 ± 6.8</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>20.4 ± 1.6</t>
+          <t>37.0 ± 2.3</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>112.4 ± 5.6</t>
+          <t>187.2 ± 5.7</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>50.6 ± 1.4</t>
+          <t>83.8 ± 3.3</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>4.0 ± 0.8</t>
+          <t>6.0 ± 0.8</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3009,37 +3009,37 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>49506.6 ± 129.5</t>
+          <t>82592.4 ± 161.6</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>36792.6 ± 139.6</t>
+          <t>61402.6 ± 130.5</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>186.0 ± 7.8</t>
+          <t>316.4 ± 7.4</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>20.2 ± 1.7</t>
+          <t>37.1 ± 2.3</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>111.4 ± 5.7</t>
+          <t>187.9 ± 5.5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>50.2 ± 1.9</t>
+          <t>83.9 ± 3.3</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>4.0 ± 0.8</t>
+          <t>6.0 ± 0.8</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3064,37 +3064,37 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>49586.4 ± 133.2</t>
+          <t>82724.8 ± 164.2</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>36636.2 ± 136.5</t>
+          <t>61165.5 ± 132.6</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>185.4 ± 8.0</t>
+          <t>315.1 ± 7.7</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>20.8 ± 2.0</t>
+          <t>36.8 ± 2.2</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>110.4 ± 5.7</t>
+          <t>187.8 ± 5.3</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>49.8 ± 2.1</t>
+          <t>84.2 ± 3.2</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>4.4 ± 1.0</t>
+          <t>5.9 ± 0.8</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3119,37 +3119,37 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>49637.2 ± 130.1</t>
+          <t>82813.6 ± 162.3</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>36466.8 ± 143.3</t>
+          <t>60888.3 ± 135.7</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>186.6 ± 9.2</t>
+          <t>315.4 ± 7.5</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>20.6 ± 1.5</t>
+          <t>36.6 ± 2.1</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>111.2 ± 6.3</t>
+          <t>188.1 ± 4.9</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>50.0 ± 2.8</t>
+          <t>84.8 ± 3.3</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>4.8 ± 1.1</t>
+          <t>6.0 ± 0.8</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3174,37 +3174,37 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>49597.2 ± 131.2</t>
+          <t>82744.2 ± 165.6</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>36196.4 ± 151.6</t>
+          <t>60469.2 ± 140.8</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>186.4 ± 9.6</t>
+          <t>315.6 ± 7.9</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>20.0 ± 1.7</t>
+          <t>36.5 ± 2.1</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>110.2 ± 6.6</t>
+          <t>188.1 ± 5.5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>51.2 ± 2.5</t>
+          <t>85.0 ± 3.1</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>5.0 ± 1.0</t>
+          <t>6.0 ± 0.9</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3229,37 +3229,37 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>49508.4 ± 134.2</t>
+          <t>82631.7 ± 165.9</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>35904.0 ± 146.5</t>
+          <t>59990.5 ± 141.5</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>187.0 ± 9.6</t>
+          <t>317.4 ± 8.1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>20.0 ± 1.5</t>
+          <t>36.6 ± 2.3</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>110.0 ± 6.5</t>
+          <t>189.2 ± 5.1</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>52.0 ± 2.4</t>
+          <t>85.7 ± 3.3</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>5.0 ± 1.0</t>
+          <t>6.0 ± 0.9</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3284,37 +3284,37 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>49396.4 ± 143.7</t>
+          <t>82449.8 ± 167.7</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>35627.2 ± 150.2</t>
+          <t>59497.2 ± 144.8</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>185.2 ± 9.0</t>
+          <t>317.1 ± 7.6</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>19.8 ± 1.5</t>
+          <t>36.0 ± 2.3</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>109.4 ± 6.2</t>
+          <t>189.2 ± 5.1</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>51.2 ± 2.6</t>
+          <t>85.5 ± 3.1</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>4.8 ± 1.1</t>
+          <t>6.2 ± 0.9</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3339,37 +3339,37 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>49265.6 ± 139.8</t>
+          <t>82230.8 ± 172.3</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>35251.6 ± 143.1</t>
+          <t>58845.5 ± 144.8</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>185.6 ± 8.5</t>
+          <t>316.3 ± 7.3</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>20.0 ± 1.8</t>
+          <t>36.4 ± 2.5</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>109.8 ± 5.7</t>
+          <t>187.7 ± 5.1</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>51.0 ± 2.5</t>
+          <t>86.0 ± 2.9</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>4.8 ± 1.1</t>
+          <t>6.2 ± 0.9</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3394,37 +3394,37 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>49165.4 ± 139.5</t>
+          <t>82047.0 ± 166.4</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>34899.0 ± 129.0</t>
+          <t>58251.8 ± 140.6</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>184.8 ± 8.0</t>
+          <t>314.9 ± 7.4</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>19.6 ± 1.7</t>
+          <t>36.5 ± 2.5</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>108.8 ± 5.7</t>
+          <t>186.4 ± 5.1</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>51.2 ± 2.9</t>
+          <t>85.8 ± 2.9</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>5.2 ± 1.1</t>
+          <t>6.2 ± 0.9</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3449,37 +3449,37 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>49074.8 ± 140.0</t>
+          <t>81918.4 ± 170.0</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>34564.0 ± 127.3</t>
+          <t>57703.6 ± 144.6</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>185.4 ± 8.3</t>
+          <t>312.6 ± 7.0</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>19.2 ± 1.8</t>
+          <t>36.7 ± 2.5</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>108.4 ± 5.9</t>
+          <t>184.7 ± 4.8</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>52.6 ± 2.4</t>
+          <t>85.2 ± 2.8</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>5.2 ± 1.1</t>
+          <t>6.0 ± 0.9</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3504,37 +3504,37 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>48942.8 ± 137.6</t>
+          <t>81712.7 ± 167.3</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>34177.0 ± 121.1</t>
+          <t>57072.6 ± 135.8</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>183.2 ± 8.5</t>
+          <t>310.6 ± 7.4</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>18.2 ± 2.1</t>
+          <t>36.6 ± 2.6</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>106.6 ± 6.2</t>
+          <t>183.3 ± 5.3</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>53.2 ± 2.5</t>
+          <t>84.8 ± 3.0</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>5.2 ± 1.1</t>
+          <t>6.0 ± 1.0</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3559,37 +3559,37 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>48783.0 ± 138.9</t>
+          <t>81444.6 ± 167.7</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>33774.6 ± 117.7</t>
+          <t>56420.9 ± 139.1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>185.4 ± 9.1</t>
+          <t>308.9 ± 7.6</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>17.8 ± 2.3</t>
+          <t>36.8 ± 2.7</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>108.6 ± 7.1</t>
+          <t>181.7 ± 5.6</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>53.6 ± 2.4</t>
+          <t>84.3 ± 3.0</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>5.4 ± 1.1</t>
+          <t>6.0 ± 0.9</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3614,37 +3614,37 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>48671.8 ± 136.4</t>
+          <t>81239.9 ± 163.7</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>33434.4 ± 112.3</t>
+          <t>55834.1 ± 133.6</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>182.2 ± 8.9</t>
+          <t>306.5 ± 7.5</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>18.0 ± 2.1</t>
+          <t>36.5 ± 2.6</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>106.0 ± 6.9</t>
+          <t>180.2 ± 5.3</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>52.6 ± 1.8</t>
+          <t>83.9 ± 3.3</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>5.6 ± 1.2</t>
+          <t>6.0 ± 0.9</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3669,37 +3669,37 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>48548.2 ± 141.0</t>
+          <t>81020.4 ± 170.5</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>33100.6 ± 111.0</t>
+          <t>55244.0 ± 136.3</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>181.0 ± 9.4</t>
+          <t>302.4 ± 7.1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>17.6 ± 1.9</t>
+          <t>36.0 ± 2.7</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>105.2 ± 7.4</t>
+          <t>177.2 ± 5.1</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>52.4 ± 1.2</t>
+          <t>83.4 ± 2.9</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>5.8 ± 1.2</t>
+          <t>5.8 ± 0.9</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3724,37 +3724,37 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>48433.6 ± 142.3</t>
+          <t>80856.6 ± 163.0</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>32780.2 ± 113.0</t>
+          <t>54748.3 ± 131.1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>178.4 ± 8.5</t>
+          <t>298.9 ± 7.1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>17.8 ± 1.8</t>
+          <t>35.6 ± 2.5</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>102.2 ± 7.2</t>
+          <t>174.8 ± 5.1</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>52.4 ± 1.7</t>
+          <t>82.5 ± 2.8</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>6.0 ± 1.0</t>
+          <t>6.0 ± 0.9</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3779,37 +3779,37 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>48332.0 ± 147.6</t>
+          <t>80671.9 ± 161.3</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>32476.2 ± 123.4</t>
+          <t>54231.6 ± 131.1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>178.8 ± 9.2</t>
+          <t>295.9 ± 7.3</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>17.4 ± 1.4</t>
+          <t>35.0 ± 2.5</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>102.8 ± 8.0</t>
+          <t>173.6 ± 5.3</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>52.6 ± 1.6</t>
+          <t>81.7 ± 2.5</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>6.0 ± 1.0</t>
+          <t>5.8 ± 0.9</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3834,37 +3834,37 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>48215.2 ± 152.4</t>
+          <t>80483.9 ± 161.1</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>32186.4 ± 130.7</t>
+          <t>53746.1 ± 126.5</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>178.0 ± 10.0</t>
+          <t>292.9 ± 6.7</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>17.4 ± 1.6</t>
+          <t>34.5 ± 2.4</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>103.4 ± 8.7</t>
+          <t>172.2 ± 4.7</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>52.0 ± 1.5</t>
+          <t>80.8 ± 2.8</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>5.2 ± 0.9</t>
+          <t>5.5 ± 0.8</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3889,37 +3889,37 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>48133.8 ± 165.1</t>
+          <t>80360.4 ± 164.0</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>31948.0 ± 136.4</t>
+          <t>53348.6 ± 130.0</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>174.8 ± 9.4</t>
+          <t>290.2 ± 6.3</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>17.0 ± 1.6</t>
+          <t>33.5 ± 2.6</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>101.6 ± 8.3</t>
+          <t>170.3 ± 4.5</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>50.6 ± 1.9</t>
+          <t>81.2 ± 2.8</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>5.6 ± 0.8</t>
+          <t>5.2 ± 0.8</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3944,37 +3944,37 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>48059.8 ± 158.4</t>
+          <t>80244.8 ± 165.0</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>31721.0 ± 133.4</t>
+          <t>52982.1 ± 133.5</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>171.6 ± 8.2</t>
+          <t>288.1 ± 6.5</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>16.2 ± 1.5</t>
+          <t>33.4 ± 2.7</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>99.6 ± 7.3</t>
+          <t>168.4 ± 4.7</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>50.2 ± 2.1</t>
+          <t>81.0 ± 2.7</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>5.6 ± 0.8</t>
+          <t>5.2 ± 0.9</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3999,37 +3999,37 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>48005.4 ± 167.8</t>
+          <t>80153.0 ± 171.5</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>31530.6 ± 137.7</t>
+          <t>52694.2 ± 135.4</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>168.6 ± 7.9</t>
+          <t>285.1 ± 6.5</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>16.0 ± 1.4</t>
+          <t>32.8 ± 2.6</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>98.4 ± 7.5</t>
+          <t>166.4 ± 4.7</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>48.4 ± 2.0</t>
+          <t>80.8 ± 2.6</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>5.8 ± 0.8</t>
+          <t>5.1 ± 0.8</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4054,37 +4054,37 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>47914.6 ± 179.8</t>
+          <t>79990.5 ± 171.6</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>31333.8 ± 144.4</t>
+          <t>52345.7 ± 137.8</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>166.0 ± 7.2</t>
+          <t>282.1 ± 6.1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>16.0 ± 1.5</t>
+          <t>32.1 ± 2.6</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>97.0 ± 7.1</t>
+          <t>164.8 ± 4.5</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>47.2 ± 1.7</t>
+          <t>80.2 ± 2.6</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>5.8 ± 0.8</t>
+          <t>5.0 ± 0.9</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4109,37 +4109,37 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>47792.6 ± 189.9</t>
+          <t>79786.1 ± 177.4</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>31106.2 ± 154.3</t>
+          <t>51983.8 ± 144.0</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>164.2 ± 6.9</t>
+          <t>279.6 ± 5.8</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>15.8 ± 1.5</t>
+          <t>31.7 ± 2.6</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>94.8 ± 6.7</t>
+          <t>163.4 ± 4.5</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>48.0 ± 1.4</t>
+          <t>79.4 ± 2.7</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>5.6 ± 0.7</t>
+          <t>5.1 ± 1.0</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4164,37 +4164,37 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>47686.2 ± 190.5</t>
+          <t>79602.9 ± 178.4</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>30901.8 ± 156.8</t>
+          <t>51635.6 ± 149.5</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>160.6 ± 7.1</t>
+          <t>277.5 ± 5.9</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>15.6 ± 1.6</t>
+          <t>31.7 ± 2.5</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>93.0 ± 6.5</t>
+          <t>162.1 ± 4.5</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>46.6 ± 0.9</t>
+          <t>78.6 ± 2.9</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>5.4 ± 0.5</t>
+          <t>5.2 ± 1.0</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4219,37 +4219,37 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>47598.0 ± 188.5</t>
+          <t>79424.1 ± 182.8</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>30665.0 ± 160.0</t>
+          <t>51262.8 ± 147.4</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>159.2 ± 7.3</t>
+          <t>274.1 ± 5.6</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>15.6 ± 1.8</t>
+          <t>31.9 ± 2.4</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>91.8 ± 6.5</t>
+          <t>159.8 ± 4.7</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>46.2 ± 0.9</t>
+          <t>77.3 ± 3.0</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>5.6 ± 0.5</t>
+          <t>5.0 ± 1.0</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4274,37 +4274,37 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>47447.4 ± 192.8</t>
+          <t>79211.4 ± 180.9</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>30434.6 ± 151.1</t>
+          <t>50880.7 ± 145.3</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>157.8 ± 7.7</t>
+          <t>271.9 ± 5.6</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>15.0 ± 1.8</t>
+          <t>31.6 ± 2.4</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>91.6 ± 6.8</t>
+          <t>158.6 ± 4.8</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>45.8 ± 1.0</t>
+          <t>77.0 ± 3.1</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>5.4 ± 0.5</t>
+          <t>4.8 ± 1.0</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4329,37 +4329,37 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>47153.4 ± 201.2</t>
+          <t>78721.6 ± 181.8</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>30205.2 ± 158.2</t>
+          <t>50478.8 ± 145.5</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>155.8 ± 7.1</t>
+          <t>268.4 ± 6.2</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>14.8 ± 2.0</t>
+          <t>31.4 ± 2.2</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>90.0 ± 6.4</t>
+          <t>156.6 ± 5.3</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>45.8 ± 0.6</t>
+          <t>75.7 ± 3.1</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>5.2 ± 0.6</t>
+          <t>4.8 ± 1.0</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4384,37 +4384,37 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>46836.4 ± 192.4</t>
+          <t>78241.9 ± 186.1</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>29934.0 ± 154.5</t>
+          <t>50059.9 ± 146.5</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>153.6 ± 7.4</t>
+          <t>265.2 ± 6.6</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>14.0 ± 2.0</t>
+          <t>30.4 ± 2.2</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>89.2 ± 6.3</t>
+          <t>155.5 ± 5.7</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>45.6 ± 0.8</t>
+          <t>74.8 ± 3.1</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>4.8 ± 0.5</t>
+          <t>4.5 ± 0.9</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4439,37 +4439,37 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>46675.6 ± 190.0</t>
+          <t>77964.6 ± 185.2</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>29702.0 ± 149.5</t>
+          <t>49649.8 ± 146.6</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>152.4 ± 7.4</t>
+          <t>262.1 ± 6.5</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>14.2 ± 2.0</t>
+          <t>29.9 ± 1.7</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>88.4 ± 6.2</t>
+          <t>153.4 ± 6.0</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>45.0 ± 0.4</t>
+          <t>74.3 ± 3.1</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>4.8 ± 0.6</t>
+          <t>4.4 ± 0.9</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -4494,37 +4494,37 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>46567.2 ± 190.9</t>
+          <t>77809.1 ± 181.1</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>29480.6 ± 151.6</t>
+          <t>49326.1 ± 136.4</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>150.6 ± 7.9</t>
+          <t>258.2 ± 6.4</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>14.0 ± 1.7</t>
+          <t>29.4 ± 1.8</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>87.0 ± 6.4</t>
+          <t>150.5 ± 5.8</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>45.0 ± 0.9</t>
+          <t>74.2 ± 3.2</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>4.6 ± 0.6</t>
+          <t>4.2 ± 0.8</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -4549,37 +4549,37 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>46350.0 ± 192.1</t>
+          <t>77431.4 ± 185.7</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>29215.4 ± 154.6</t>
+          <t>48893.7 ± 140.6</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>146.2 ± 7.3</t>
+          <t>254.4 ± 6.5</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>13.6 ± 1.6</t>
+          <t>28.5 ± 1.7</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>83.6 ± 5.5</t>
+          <t>148.4 ± 6.1</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>44.4 ± 1.4</t>
+          <t>73.2 ± 2.9</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>4.6 ± 0.6</t>
+          <t>4.3 ± 0.8</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4604,37 +4604,37 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>46079.2 ± 194.8</t>
+          <t>76998.1 ± 190.9</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>28933.6 ± 149.4</t>
+          <t>48409.2 ± 141.9</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>144.0 ± 7.6</t>
+          <t>249.4 ± 6.1</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>13.0 ± 1.7</t>
+          <t>28.2 ± 1.7</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>83.0 ± 5.5</t>
+          <t>145.3 ± 5.9</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>43.4 ± 1.5</t>
+          <t>71.8 ± 3.0</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>4.6 ± 0.6</t>
+          <t>4.1 ± 0.8</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -4659,37 +4659,37 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>45791.6 ± 197.6</t>
+          <t>76523.5 ± 193.1</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>28637.4 ± 150.2</t>
+          <t>47907.4 ± 143.2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>141.8 ± 7.5</t>
+          <t>245.6 ± 5.9</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>13.0 ± 1.7</t>
+          <t>27.7 ± 1.7</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>81.2 ± 5.7</t>
+          <t>142.9 ± 5.6</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>43.4 ± 1.2</t>
+          <t>71.0 ± 3.0</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>4.2 ± 0.6</t>
+          <t>4.0 ± 0.8</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4714,37 +4714,37 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>45498.2 ± 200.7</t>
+          <t>76031.6 ± 189.8</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>28337.4 ± 146.0</t>
+          <t>47401.8 ± 141.7</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>139.6 ± 7.9</t>
+          <t>240.8 ± 6.0</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>13.4 ± 1.7</t>
+          <t>27.2 ± 1.9</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>79.0 ± 5.8</t>
+          <t>139.7 ± 5.4</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>43.2 ± 1.2</t>
+          <t>69.8 ± 2.8</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>4.0 ± 0.6</t>
+          <t>4.1 ± 0.8</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -4769,37 +4769,37 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>45165.4 ± 205.2</t>
+          <t>75508.2 ± 187.0</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>28039.4 ± 131.7</t>
+          <t>46899.6 ± 140.9</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>136.2 ± 7.6</t>
+          <t>235.7 ± 5.7</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>12.8 ± 1.6</t>
+          <t>26.6 ± 2.0</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>77.2 ± 5.8</t>
+          <t>136.6 ± 5.1</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>42.6 ± 1.1</t>
+          <t>68.5 ± 2.8</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>3.6 ± 0.4</t>
+          <t>4.0 ± 0.8</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4824,37 +4824,37 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>44856.6 ± 201.8</t>
+          <t>74966.2 ± 186.4</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>27725.6 ± 125.4</t>
+          <t>46378.8 ± 145.6</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>132.2 ± 7.6</t>
+          <t>231.4 ± 5.8</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>12.2 ± 1.6</t>
+          <t>26.1 ± 1.9</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>75.6 ± 5.6</t>
+          <t>133.6 ± 5.1</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>41.0 ± 1.6</t>
+          <t>67.8 ± 2.4</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>3.4 ± 0.3</t>
+          <t>3.9 ± 0.8</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4879,37 +4879,37 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>44510.6 ± 208.5</t>
+          <t>74410.1 ± 192.2</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>27380.0 ± 124.6</t>
+          <t>45857.4 ± 149.4</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>129.2 ± 7.2</t>
+          <t>227.6 ± 6.0</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>11.8 ± 1.5</t>
+          <t>25.4 ± 1.8</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>73.8 ± 5.6</t>
+          <t>131.6 ± 5.1</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>40.6 ± 1.4</t>
+          <t>66.8 ± 2.9</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>3.0 ± 0.3</t>
+          <t>3.9 ± 0.8</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4934,37 +4934,37 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>44126.6 ± 199.5</t>
+          <t>73790.6 ± 194.6</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>27059.8 ± 119.5</t>
+          <t>45305.4 ± 153.0</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>126.6 ± 6.8</t>
+          <t>223.4 ± 5.4</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>11.4 ± 1.4</t>
+          <t>24.9 ± 1.8</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>72.0 ± 5.3</t>
+          <t>128.3 ± 4.3</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>40.6 ± 1.6</t>
+          <t>66.3 ± 2.9</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2.6 ± 0.2</t>
+          <t>4.0 ± 0.8</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4989,37 +4989,37 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>43729.8 ± 205.7</t>
+          <t>73145.9 ± 198.9</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>26707.2 ± 120.2</t>
+          <t>44703.5 ± 151.6</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>123.2 ± 6.3</t>
+          <t>219.2 ± 5.0</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>11.2 ± 1.1</t>
+          <t>24.1 ± 1.8</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>69.8 ± 4.9</t>
+          <t>125.2 ± 3.8</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>39.6 ± 1.7</t>
+          <t>66.2 ± 3.1</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2.6 ± 0.2</t>
+          <t>3.9 ± 0.8</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5044,37 +5044,37 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>43374.0 ± 209.9</t>
+          <t>72512.9 ± 196.5</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>26347.0 ± 116.3</t>
+          <t>44059.7 ± 150.0</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>119.6 ± 5.5</t>
+          <t>214.1 ± 5.1</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>10.6 ± 1.1</t>
+          <t>23.6 ± 1.8</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>67.4 ± 4.7</t>
+          <t>121.8 ± 3.7</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>39.2 ± 1.6</t>
+          <t>65.0 ± 3.0</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2.4 ± 0.2</t>
+          <t>3.7 ± 0.8</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5099,37 +5099,37 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>42992.2 ± 200.9</t>
+          <t>71876.2 ± 197.9</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>25960.8 ± 121.1</t>
+          <t>43387.4 ± 151.0</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>116.0 ± 5.3</t>
+          <t>208.7 ± 5.2</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>10.8 ± 1.1</t>
+          <t>22.7 ± 1.9</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>66.0 ± 5.1</t>
+          <t>118.6 ± 4.2</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>37.2 ± 1.5</t>
+          <t>63.9 ± 2.9</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2.0 ± 0.3</t>
+          <t>3.5 ± 0.8</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5154,37 +5154,37 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>42606.8 ± 212.1</t>
+          <t>71228.4 ± 195.3</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>25569.8 ± 127.1</t>
+          <t>42691.2 ± 154.3</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>111.8 ± 5.0</t>
+          <t>204.3 ± 5.2</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>9.8 ± 1.2</t>
+          <t>21.6 ± 1.8</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>63.0 ± 5.0</t>
+          <t>115.9 ± 4.0</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>36.8 ± 1.4</t>
+          <t>63.3 ± 2.7</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2.2 ± 0.3</t>
+          <t>3.5 ± 0.8</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5209,37 +5209,37 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>42245.4 ± 211.5</t>
+          <t>70614.4 ± 197.7</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>25150.8 ± 123.1</t>
+          <t>41990.5 ± 151.5</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>110.6 ± 5.1</t>
+          <t>199.2 ± 5.1</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>9.6 ± 1.1</t>
+          <t>21.3 ± 1.9</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>61.2 ± 4.8</t>
+          <t>111.8 ± 4.2</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>37.6 ± 2.0</t>
+          <t>62.7 ± 2.5</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2.2 ± 0.3</t>
+          <t>3.4 ± 0.8</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5264,37 +5264,37 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>41873.4 ± 215.0</t>
+          <t>70011.4 ± 199.3</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>24711.6 ± 138.6</t>
+          <t>41295.7 ± 153.4</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>108.4 ± 4.9</t>
+          <t>193.9 ± 4.8</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>9.8 ± 1.2</t>
+          <t>20.4 ± 1.8</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>58.8 ± 4.5</t>
+          <t>108.4 ± 4.4</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>37.6 ± 2.3</t>
+          <t>61.9 ± 2.5</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2.2 ± 0.3</t>
+          <t>3.1 ± 0.8</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5319,37 +5319,37 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>41508.8 ± 213.1</t>
+          <t>69352.8 ± 197.8</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>24284.0 ± 139.5</t>
+          <t>40581.8 ± 146.8</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>102.8 ± 5.5</t>
+          <t>188.6 ± 5.1</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>9.6 ± 1.1</t>
+          <t>20.0 ± 1.8</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>55.2 ± 4.5</t>
+          <t>105.0 ± 4.7</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>35.8 ± 2.5</t>
+          <t>60.6 ± 2.6</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2.2 ± 0.3</t>
+          <t>3.0 ± 0.7</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5374,37 +5374,37 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>41123.8 ± 210.1</t>
+          <t>68711.6 ± 196.5</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>23833.4 ± 142.5</t>
+          <t>39876.3 ± 151.1</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>99.2 ± 5.2</t>
+          <t>182.1 ± 5.3</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>8.8 ± 1.0</t>
+          <t>19.1 ± 1.8</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>53.4 ± 4.2</t>
+          <t>100.5 ± 4.9</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>35.0 ± 2.5</t>
+          <t>59.7 ± 2.6</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2.0 ± 0.3</t>
+          <t>2.8 ± 0.7</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -5429,37 +5429,37 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>40745.0 ± 202.3</t>
+          <t>68069.1 ± 196.4</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>23441.6 ± 139.1</t>
+          <t>39188.4 ± 148.4</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>94.2 ± 5.3</t>
+          <t>176.4 ± 5.2</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>8.2 ± 1.1</t>
+          <t>18.9 ± 1.8</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>51.2 ± 3.8</t>
+          <t>96.5 ± 4.5</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>32.8 ± 2.5</t>
+          <t>58.5 ± 2.5</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2.0 ± 0.3</t>
+          <t>2.5 ± 0.6</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -5484,37 +5484,37 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>40365.0 ± 207.5</t>
+          <t>67416.1 ± 194.7</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>23029.8 ± 146.3</t>
+          <t>38521.4 ± 151.9</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>91.0 ± 5.1</t>
+          <t>169.7 ± 5.0</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>7.8 ± 0.9</t>
+          <t>18.2 ± 1.6</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>50.4 ± 3.6</t>
+          <t>91.8 ± 4.2</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>31.0 ± 2.7</t>
+          <t>57.2 ± 2.4</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>1.8 ± 0.3</t>
+          <t>2.5 ± 0.6</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -5539,37 +5539,37 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>39988.6 ± 205.0</t>
+          <t>66761.4 ± 196.1</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>22643.2 ± 146.5</t>
+          <t>37913.2 ± 150.0</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>85.8 ± 5.3</t>
+          <t>163.2 ± 4.8</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>7.2 ± 0.9</t>
+          <t>17.3 ± 1.6</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>46.8 ± 3.9</t>
+          <t>87.7 ± 4.0</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>30.0 ± 2.3</t>
+          <t>56.0 ± 2.6</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>1.8 ± 0.3</t>
+          <t>2.2 ± 0.5</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -5594,37 +5594,37 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>39596.8 ± 200.5</t>
+          <t>66132.4 ± 204.0</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>22307.8 ± 141.4</t>
+          <t>37395.1 ± 153.3</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>83.4 ± 5.1</t>
+          <t>158.2 ± 5.1</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>6.8 ± 0.6</t>
+          <t>16.6 ± 1.6</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>45.4 ± 3.9</t>
+          <t>84.5 ± 4.3</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>29.4 ± 2.2</t>
+          <t>54.9 ± 2.5</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>1.8 ± 0.3</t>
+          <t>2.2 ± 0.5</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -5649,37 +5649,37 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>39220.2 ± 199.6</t>
+          <t>65495.4 ± 206.9</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>22065.6 ± 141.9</t>
+          <t>36961.2 ± 151.4</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>79.0 ± 4.9</t>
+          <t>154.1 ± 5.0</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>6.8 ± 0.7</t>
+          <t>15.8 ± 1.4</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>42.2 ± 4.0</t>
+          <t>81.2 ± 4.0</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>28.4 ± 2.2</t>
+          <t>54.9 ± 2.5</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>1.6 ± 0.4</t>
+          <t>2.1 ± 0.5</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -5704,37 +5704,37 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>38852.0 ± 202.2</t>
+          <t>64872.3 ± 207.2</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>21825.6 ± 145.6</t>
+          <t>36522.8 ± 151.0</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>75.8 ± 4.7</t>
+          <t>149.1 ± 5.1</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>6.0 ± 0.8</t>
+          <t>15.5 ± 1.4</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>40.4 ± 3.8</t>
+          <t>77.5 ± 3.6</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>28.0 ± 2.0</t>
+          <t>54.0 ± 2.6</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>1.4 ± 0.4</t>
+          <t>2.0 ± 0.5</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -5759,37 +5759,37 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>38479.8 ± 210.5</t>
+          <t>64246.3 ± 209.9</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>21563.4 ± 145.4</t>
+          <t>36098.9 ± 151.6</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>72.6 ± 4.4</t>
+          <t>145.7 ± 5.0</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>6.2 ± 0.8</t>
+          <t>15.3 ± 1.4</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>37.0 ± 3.4</t>
+          <t>74.8 ± 3.5</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>28.2 ± 1.9</t>
+          <t>53.7 ± 2.4</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>1.2 ± 0.3</t>
+          <t>1.9 ± 0.5</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -5814,37 +5814,37 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>38110.8 ± 217.3</t>
+          <t>63632.6 ± 210.9</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>21358.2 ± 143.8</t>
+          <t>35742.9 ± 150.2</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>69.2 ± 4.2</t>
+          <t>141.6 ± 5.1</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>6.0 ± 0.9</t>
+          <t>14.4 ± 1.4</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>34.8 ± 3.5</t>
+          <t>72.0 ± 3.5</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>27.4 ± 1.8</t>
+          <t>53.4 ± 2.5</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>1.0 ± 0.3</t>
+          <t>1.8 ± 0.4</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -5869,37 +5869,37 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>37754.6 ± 218.7</t>
+          <t>63021.2 ± 212.0</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>21162.0 ± 145.4</t>
+          <t>35410.6 ± 149.7</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>67.0 ± 4.9</t>
+          <t>136.2 ± 4.6</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>5.4 ± 0.8</t>
+          <t>13.7 ± 1.5</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>32.8 ± 4.0</t>
+          <t>68.7 ± 3.3</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>27.8 ± 1.5</t>
+          <t>52.2 ± 2.3</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>1.0 ± 0.3</t>
+          <t>1.8 ± 0.4</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -5924,37 +5924,37 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>37401.0 ± 221.5</t>
+          <t>62430.7 ± 213.6</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>21029.6 ± 152.6</t>
+          <t>35209.4 ± 145.0</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>65.0 ± 4.5</t>
+          <t>133.4 ± 4.9</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>4.8 ± 0.8</t>
+          <t>13.3 ± 1.4</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>31.2 ± 3.8</t>
+          <t>66.8 ± 3.4</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>27.8 ± 1.4</t>
+          <t>51.8 ± 2.4</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>1.2 ± 0.3</t>
+          <t>1.6 ± 0.4</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -5979,37 +5979,37 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>37035.6 ± 221.1</t>
+          <t>61842.2 ± 212.5</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>20951.0 ± 153.5</t>
+          <t>35083.9 ± 144.1</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>62.2 ± 4.5</t>
+          <t>131.0 ± 4.5</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>4.2 ± 0.6</t>
+          <t>12.8 ± 1.4</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>29.6 ± 4.1</t>
+          <t>65.3 ± 3.2</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>27.2 ± 1.4</t>
+          <t>51.4 ± 2.2</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>1.2 ± 0.3</t>
+          <t>1.6 ± 0.4</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6034,37 +6034,37 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>36700.8 ± 223.3</t>
+          <t>61243.7 ± 214.1</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>20909.0 ± 153.4</t>
+          <t>34993.7 ± 143.6</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>60.6 ± 4.2</t>
+          <t>129.3 ± 4.7</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>3.8 ± 0.5</t>
+          <t>12.4 ± 1.4</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>28.0 ± 3.8</t>
+          <t>64.0 ± 3.4</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>27.6 ± 1.1</t>
+          <t>51.3 ± 2.2</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>1.2 ± 0.3</t>
+          <t>1.6 ± 0.4</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6089,37 +6089,37 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>36319.0 ± 211.7</t>
+          <t>60637.1 ± 210.8</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>20825.4 ± 156.1</t>
+          <t>34881.4 ± 143.3</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>59.8 ± 3.8</t>
+          <t>127.3 ± 4.5</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>3.8 ± 0.5</t>
+          <t>12.2 ± 1.3</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>27.4 ± 3.4</t>
+          <t>62.4 ± 3.4</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>27.4 ± 1.0</t>
+          <t>51.3 ± 2.1</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>1.2 ± 0.3</t>
+          <t>1.4 ± 0.4</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6144,37 +6144,37 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>35953.2 ± 219.8</t>
+          <t>60028.4 ± 213.9</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>20733.6 ± 164.3</t>
+          <t>34709.8 ± 147.4</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>58.4 ± 3.3</t>
+          <t>124.6 ± 4.3</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>3.8 ± 0.5</t>
+          <t>11.7 ± 1.3</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>25.8 ± 3.1</t>
+          <t>60.7 ± 3.4</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>27.6 ± 1.4</t>
+          <t>50.8 ± 1.9</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>1.2 ± 0.3</t>
+          <t>1.4 ± 0.4</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6199,37 +6199,37 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>35569.4 ± 216.9</t>
+          <t>59419.4 ± 213.2</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>20602.2 ± 159.0</t>
+          <t>34485.6 ± 142.6</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>57.4 ± 3.2</t>
+          <t>121.9 ± 4.1</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>3.8 ± 0.5</t>
+          <t>11.3 ± 1.3</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>24.8 ± 2.8</t>
+          <t>58.5 ± 3.3</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>27.6 ± 1.4</t>
+          <t>50.7 ± 2.1</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>1.2 ± 0.3</t>
+          <t>1.4 ± 0.4</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6254,37 +6254,37 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>35196.6 ± 212.8</t>
+          <t>58810.0 ± 215.4</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>20470.0 ± 158.0</t>
+          <t>34293.4 ± 143.6</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>55.4 ± 2.8</t>
+          <t>120.0 ± 4.1</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>3.2 ± 0.4</t>
+          <t>11.1 ± 1.2</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>23.4 ± 2.4</t>
+          <t>57.2 ± 3.3</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>27.8 ± 1.7</t>
+          <t>50.2 ± 2.1</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>1.0 ± 0.3</t>
+          <t>1.4 ± 0.4</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -6309,37 +6309,37 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>34843.0 ± 208.4</t>
+          <t>58200.8 ± 216.4</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>20352.8 ± 148.8</t>
+          <t>34086.6 ± 143.0</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>54.8 ± 3.3</t>
+          <t>116.9 ± 3.8</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>3.0 ± 0.3</t>
+          <t>10.4 ± 1.2</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>22.6 ± 2.2</t>
+          <t>54.9 ± 3.1</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>28.2 ± 1.5</t>
+          <t>50.2 ± 2.0</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>1.0 ± 0.3</t>
+          <t>1.4 ± 0.4</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -6364,37 +6364,37 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>34474.6 ± 211.3</t>
+          <t>57590.0 ± 209.9</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>20202.4 ± 153.4</t>
+          <t>33824.0 ± 146.9</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>53.0 ± 3.6</t>
+          <t>114.8 ± 3.7</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2.8 ± 0.2</t>
+          <t>10.2 ± 1.2</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>21.2 ± 2.4</t>
+          <t>52.6 ± 2.8</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>28.0 ± 1.8</t>
+          <t>50.6 ± 2.2</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>1.0 ± 0.3</t>
+          <t>1.3 ± 0.4</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -6419,37 +6419,37 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>34096.8 ± 208.5</t>
+          <t>56960.9 ± 209.0</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>20020.6 ± 150.9</t>
+          <t>33533.3 ± 146.2</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>50.4 ± 2.9</t>
+          <t>111.5 ± 4.0</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>3.0 ± 0.3</t>
+          <t>9.6 ± 1.2</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>19.4 ± 2.0</t>
+          <t>50.2 ± 2.9</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>27.0 ± 1.5</t>
+          <t>50.4 ± 2.0</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>1.0 ± 0.3</t>
+          <t>1.4 ± 0.4</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -6474,37 +6474,37 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>33726.2 ± 211.1</t>
+          <t>56339.2 ± 212.8</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>19811.8 ± 152.1</t>
+          <t>33177.0 ± 153.7</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>48.2 ± 2.6</t>
+          <t>108.7 ± 4.0</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2.4 ± 0.3</t>
+          <t>9.2 ± 1.2</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>17.4 ± 1.6</t>
+          <t>48.5 ± 2.9</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>27.4 ± 1.5</t>
+          <t>49.8 ± 2.0</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>1.0 ± 0.3</t>
+          <t>1.3 ± 0.4</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -6529,37 +6529,37 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>33340.2 ± 219.5</t>
+          <t>55710.8 ± 212.7</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>19594.0 ± 158.9</t>
+          <t>32810.8 ± 156.3</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>48.4 ± 2.6</t>
+          <t>105.8 ± 3.5</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2.6 ± 0.2</t>
+          <t>8.8 ± 1.2</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>17.4 ± 1.6</t>
+          <t>46.6 ± 2.7</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>27.4 ± 1.5</t>
+          <t>49.2 ± 2.1</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>1.0 ± 0.3</t>
+          <t>1.1 ± 0.3</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -6584,37 +6584,37 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>32961.6 ± 220.2</t>
+          <t>55073.9 ± 214.3</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>19381.6 ± 159.5</t>
+          <t>32447.1 ± 157.5</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>48.6 ± 3.0</t>
+          <t>101.7 ± 4.0</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2.8 ± 0.2</t>
+          <t>8.1 ± 1.0</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>17.6 ± 1.6</t>
+          <t>44.4 ± 2.8</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>27.2 ± 1.8</t>
+          <t>48.4 ± 2.1</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>1.0 ± 0.3</t>
+          <t>0.8 ± 0.2</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -6639,37 +6639,37 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>32598.0 ± 217.3</t>
+          <t>54435.4 ± 209.9</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>19151.8 ± 160.0</t>
+          <t>32029.0 ± 156.3</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>49.2 ± 2.8</t>
+          <t>98.0 ± 3.9</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>3.0 ± 0.3</t>
+          <t>8.1 ± 1.2</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>18.2 ± 1.8</t>
+          <t>41.5 ± 2.7</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>27.0 ± 1.7</t>
+          <t>47.8 ± 2.0</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>1.0 ± 0.3</t>
+          <t>0.8 ± 0.2</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -6694,37 +6694,37 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>32206.4 ± 221.4</t>
+          <t>53813.8 ± 208.7</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>18895.2 ± 163.5</t>
+          <t>31615.4 ± 154.5</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>50.0 ± 2.6</t>
+          <t>94.3 ± 3.9</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>3.4 ± 0.2</t>
+          <t>7.6 ± 1.1</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>18.6 ± 1.7</t>
+          <t>38.5 ± 2.5</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>27.0 ± 1.5</t>
+          <t>47.5 ± 2.1</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>1.0 ± 0.3</t>
+          <t>0.8 ± 0.2</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -6749,37 +6749,37 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>31801.6 ± 213.2</t>
+          <t>53196.9 ± 209.2</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>18603.8 ± 155.4</t>
+          <t>31150.9 ± 149.0</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>49.0 ± 2.4</t>
+          <t>90.0 ± 3.8</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>3.4 ± 0.2</t>
+          <t>6.8 ± 1.1</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>18.4 ± 1.7</t>
+          <t>35.4 ± 2.3</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>26.2 ± 1.4</t>
+          <t>47.0 ± 2.1</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>1.0 ± 0.3</t>
+          <t>0.8 ± 0.2</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -6804,37 +6804,37 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>31424.6 ± 217.4</t>
+          <t>52580.9 ± 211.6</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>18351.2 ± 151.0</t>
+          <t>30739.6 ± 152.1</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>48.2 ± 2.4</t>
+          <t>86.2 ± 3.9</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>3.2 ± 0.2</t>
+          <t>6.0 ± 1.0</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>19.0 ± 1.5</t>
+          <t>32.7 ± 2.2</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>25.0 ± 1.3</t>
+          <t>46.7 ± 2.3</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>1.0 ± 0.3</t>
+          <t>0.8 ± 0.2</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -6859,37 +6859,37 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>31035.4 ± 220.3</t>
+          <t>51974.0 ± 210.7</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>18102.0 ± 140.1</t>
+          <t>30339.2 ± 149.1</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>49.0 ± 2.6</t>
+          <t>82.7 ± 3.7</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>3.2 ± 0.2</t>
+          <t>5.5 ± 0.9</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>19.2 ± 1.4</t>
+          <t>30.9 ± 1.9</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>25.6 ± 1.3</t>
+          <t>45.6 ± 2.3</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>1.0 ± 0.3</t>
+          <t>0.8 ± 0.2</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -6914,37 +6914,37 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>30692.0 ± 216.9</t>
+          <t>51371.2 ± 212.9</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>17856.2 ± 133.8</t>
+          <t>29940.9 ± 149.5</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>48.0 ± 2.3</t>
+          <t>79.5 ± 3.3</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>3.4 ± 0.2</t>
+          <t>5.0 ± 1.0</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>18.8 ± 1.3</t>
+          <t>29.1 ± 1.6</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>24.8 ± 1.0</t>
+          <t>44.8 ± 2.3</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>1.0 ± 0.3</t>
+          <t>0.7 ± 0.2</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -6969,37 +6969,37 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>30318.2 ± 215.8</t>
+          <t>50768.2 ± 212.7</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>17634.8 ± 142.9</t>
+          <t>29566.3 ± 151.4</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>47.4 ± 2.4</t>
+          <t>79.4 ± 2.9</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>3.4 ± 0.2</t>
+          <t>5.0 ± 0.9</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>18.4 ± 1.3</t>
+          <t>29.4 ± 1.5</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>24.6 ± 1.0</t>
+          <t>44.4 ± 2.1</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>1.0 ± 0.3</t>
+          <t>0.7 ± 0.2</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7024,37 +7024,37 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>29938.4 ± 216.2</t>
+          <t>50152.8 ± 211.7</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>17427.6 ± 148.2</t>
+          <t>29205.9 ± 152.8</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>46.8 ± 2.4</t>
+          <t>78.6 ± 2.7</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>3.6 ± 0.2</t>
+          <t>5.0 ± 0.9</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>18.2 ± 1.2</t>
+          <t>28.8 ± 1.6</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>24.2 ± 1.1</t>
+          <t>44.1 ± 1.8</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>0.8 ± 0.2</t>
+          <t>0.7 ± 0.2</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7079,37 +7079,37 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>29580.4 ± 216.3</t>
+          <t>49536.3 ± 207.7</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>17185.4 ± 146.9</t>
+          <t>28804.7 ± 149.4</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>46.6 ± 2.0</t>
+          <t>77.5 ± 2.5</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>3.8 ± 0.3</t>
+          <t>4.8 ± 0.9</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>18.0 ± 1.1</t>
+          <t>28.4 ± 1.6</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>24.0 ± 0.8</t>
+          <t>43.5 ± 1.7</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>0.8 ± 0.2</t>
+          <t>0.7 ± 0.2</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7134,37 +7134,37 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>29211.6 ± 210.9</t>
+          <t>48926.1 ± 213.8</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>16967.6 ± 146.4</t>
+          <t>28443.5 ± 153.2</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>46.2 ± 1.8</t>
+          <t>76.5 ± 2.8</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>3.8 ± 0.3</t>
+          <t>4.7 ± 0.9</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>18.2 ± 1.2</t>
+          <t>27.6 ± 1.6</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>23.6 ± 0.7</t>
+          <t>43.5 ± 1.8</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>0.6 ± 0.2</t>
+          <t>0.7 ± 0.2</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7189,37 +7189,37 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>28854.2 ± 206.9</t>
+          <t>48325.2 ± 211.4</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>16758.0 ± 137.1</t>
+          <t>28099.4 ± 151.5</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>45.0 ± 1.7</t>
+          <t>74.8 ± 2.9</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>3.8 ± 0.3</t>
+          <t>4.7 ± 0.8</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>17.8 ± 1.2</t>
+          <t>27.2 ± 1.6</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>22.8 ± 0.6</t>
+          <t>42.2 ± 2.0</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>0.6 ± 0.2</t>
+          <t>0.7 ± 0.2</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -7244,37 +7244,37 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>28485.8 ± 215.1</t>
+          <t>47738.6 ± 211.0</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>16521.4 ± 136.8</t>
+          <t>27697.7 ± 152.0</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>44.6 ± 1.4</t>
+          <t>74.2 ± 3.0</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>3.8 ± 0.3</t>
+          <t>4.6 ± 0.8</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>17.4 ± 1.2</t>
+          <t>26.8 ± 1.7</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>22.8 ± 0.5</t>
+          <t>42.1 ± 1.9</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>0.6 ± 0.2</t>
+          <t>0.7 ± 0.2</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -7299,37 +7299,37 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>28137.8 ± 212.7</t>
+          <t>47173.7 ± 206.2</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>16315.4 ± 134.0</t>
+          <t>27363.5 ± 150.5</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>44.8 ± 1.6</t>
+          <t>73.2 ± 2.8</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>3.6 ± 0.2</t>
+          <t>4.5 ± 0.8</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>17.6 ± 1.4</t>
+          <t>26.6 ± 1.7</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>23.0 ± 0.6</t>
+          <t>41.4 ± 1.9</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>0.6 ± 0.2</t>
+          <t>0.7 ± 0.2</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -7354,37 +7354,37 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>27787.6 ± 209.7</t>
+          <t>46604.2 ± 203.8</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>16128.0 ± 132.4</t>
+          <t>27062.9 ± 148.7</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>43.8 ± 1.7</t>
+          <t>72.0 ± 2.7</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>3.4 ± 0.3</t>
+          <t>4.5 ± 0.8</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>17.2 ± 1.3</t>
+          <t>26.1 ± 1.7</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>22.6 ± 0.5</t>
+          <t>40.8 ± 1.8</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>0.6 ± 0.2</t>
+          <t>0.7 ± 0.2</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -7409,37 +7409,37 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>27450.6 ± 205.5</t>
+          <t>46045.2 ± 203.9</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>15935.6 ± 127.7</t>
+          <t>26775.4 ± 144.7</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>43.2 ± 2.1</t>
+          <t>71.5 ± 2.6</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>3.4 ± 0.5</t>
+          <t>4.4 ± 0.7</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>16.8 ± 1.4</t>
+          <t>25.6 ± 1.7</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>22.4 ± 0.8</t>
+          <t>40.8 ± 1.9</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>0.6 ± 0.2</t>
+          <t>0.8 ± 0.2</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -7464,37 +7464,37 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>27107.4 ± 210.5</t>
+          <t>45474.8 ± 199.3</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>15770.2 ± 130.8</t>
+          <t>26481.0 ± 139.7</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>42.4 ± 1.8</t>
+          <t>70.4 ± 2.9</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>3.4 ± 0.5</t>
+          <t>4.3 ± 0.8</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>15.8 ± 1.4</t>
+          <t>25.1 ± 2.0</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>22.6 ± 1.0</t>
+          <t>40.1 ± 2.1</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>0.6 ± 0.2</t>
+          <t>0.8 ± 0.2</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -7519,37 +7519,37 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>26791.4 ± 221.6</t>
+          <t>44962.6 ± 202.4</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>15615.2 ± 128.4</t>
+          <t>26221.8 ± 141.2</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>41.4 ± 1.7</t>
+          <t>69.8 ± 2.9</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>3.4 ± 0.5</t>
+          <t>4.2 ± 0.7</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>15.2 ± 1.4</t>
+          <t>24.6 ± 2.0</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>22.4 ± 0.8</t>
+          <t>40.1 ± 2.1</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>0.4 ± 0.2</t>
+          <t>0.8 ± 0.2</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -7574,37 +7574,37 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>26471.6 ± 223.2</t>
+          <t>44472.8 ± 205.5</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>15447.8 ± 139.4</t>
+          <t>25969.7 ± 141.8</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>40.8 ± 1.9</t>
+          <t>68.7 ± 2.7</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>3.2 ± 0.5</t>
+          <t>4.2 ± 0.7</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>15.2 ± 1.3</t>
+          <t>24.4 ± 1.8</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>22.0 ± 1.0</t>
+          <t>39.1 ± 2.0</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>0.4 ± 0.2</t>
+          <t>0.9 ± 0.2</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -7629,37 +7629,37 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>26183.8 ± 226.0</t>
+          <t>44013.2 ± 207.9</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>15295.6 ± 139.4</t>
+          <t>25707.8 ± 141.2</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>40.0 ± 2.2</t>
+          <t>67.9 ± 2.8</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2.8 ± 0.5</t>
+          <t>4.2 ± 0.6</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>14.8 ± 1.3</t>
+          <t>24.1 ± 1.9</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>22.0 ± 1.3</t>
+          <t>38.9 ± 2.2</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>0.4 ± 0.2</t>
+          <t>0.8 ± 0.2</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -7684,37 +7684,37 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>25933.0 ± 221.4</t>
+          <t>43555.9 ± 203.3</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>15158.6 ± 143.6</t>
+          <t>25470.2 ± 138.0</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>40.4 ± 2.3</t>
+          <t>66.7 ± 2.8</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2.6 ± 0.4</t>
+          <t>3.9 ± 0.6</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>14.8 ± 1.5</t>
+          <t>23.4 ± 1.9</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>22.8 ± 1.0</t>
+          <t>38.7 ± 2.2</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>0.2 ± 0.2</t>
+          <t>0.8 ± 0.2</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -7739,37 +7739,37 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>25666.6 ± 225.2</t>
+          <t>43107.8 ± 206.3</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>15015.8 ± 142.3</t>
+          <t>25235.0 ± 138.0</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>39.4 ± 2.5</t>
+          <t>65.5 ± 2.7</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2.4 ± 0.4</t>
+          <t>3.8 ± 0.6</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>14.2 ± 1.3</t>
+          <t>23.1 ± 1.9</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>22.6 ± 1.0</t>
+          <t>37.9 ± 2.2</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>0.2 ± 0.2</t>
+          <t>0.8 ± 0.2</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -7794,37 +7794,37 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>25403.8 ± 224.3</t>
+          <t>42679.5 ± 203.5</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>14859.0 ± 144.0</t>
+          <t>24992.0 ± 137.9</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>39.6 ± 2.8</t>
+          <t>64.8 ± 2.7</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2.4 ± 0.4</t>
+          <t>3.7 ± 0.6</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>13.8 ± 1.4</t>
+          <t>22.8 ± 1.7</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>23.2 ± 1.1</t>
+          <t>37.5 ± 2.2</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>0.2 ± 0.2</t>
+          <t>0.8 ± 0.2</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -7849,37 +7849,37 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>25159.6 ± 226.9</t>
+          <t>42264.8 ± 205.3</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>14700.6 ± 143.4</t>
+          <t>24747.5 ± 141.0</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>39.2 ± 2.7</t>
+          <t>64.0 ± 2.8</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2.4 ± 0.4</t>
+          <t>3.7 ± 0.7</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>13.6 ± 1.2</t>
+          <t>22.6 ± 1.7</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>23.0 ± 1.2</t>
+          <t>37.0 ± 2.3</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>0.2 ± 0.2</t>
+          <t>0.8 ± 0.2</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -7904,37 +7904,37 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>24922.0 ± 228.9</t>
+          <t>41874.3 ± 208.1</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>14537.0 ± 135.4</t>
+          <t>24507.6 ± 141.8</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>39.2 ± 3.0</t>
+          <t>63.2 ± 2.6</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2.4 ± 0.4</t>
+          <t>3.6 ± 0.6</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>13.8 ± 1.4</t>
+          <t>22.4 ± 1.7</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>22.8 ± 1.4</t>
+          <t>36.5 ± 2.3</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>0.2 ± 0.2</t>
+          <t>0.8 ± 0.2</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -7959,37 +7959,37 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>24713.6 ± 226.7</t>
+          <t>41500.9 ± 208.5</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>14400.6 ± 135.5</t>
+          <t>24249.5 ± 145.4</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>39.2 ± 3.8</t>
+          <t>62.7 ± 2.8</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2.4 ± 0.4</t>
+          <t>3.6 ± 0.6</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>14.0 ± 1.5</t>
+          <t>22.4 ± 1.8</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>22.6 ± 2.0</t>
+          <t>35.9 ± 2.6</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>0.2 ± 0.2</t>
+          <t>0.8 ± 0.2</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8014,37 +8014,37 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>24517.6 ± 223.1</t>
+          <t>41151.0 ± 202.6</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>14262.6 ± 127.3</t>
+          <t>24003.8 ± 142.1</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>39.0 ± 3.4</t>
+          <t>62.0 ± 2.6</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2.2 ± 0.3</t>
+          <t>3.6 ± 0.6</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>13.6 ± 1.5</t>
+          <t>21.9 ± 1.7</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>23.0 ± 1.8</t>
+          <t>35.7 ± 2.4</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>0.2 ± 0.2</t>
+          <t>0.8 ± 0.2</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8069,37 +8069,37 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>24298.4 ± 230.4</t>
+          <t>40805.5 ± 199.6</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>14117.4 ± 129.1</t>
+          <t>23753.8 ± 140.5</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>39.0 ± 3.8</t>
+          <t>62.0 ± 2.4</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2.2 ± 0.4</t>
+          <t>3.6 ± 0.6</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>14.2 ± 1.6</t>
+          <t>21.6 ± 1.6</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>22.4 ± 2.0</t>
+          <t>36.0 ± 2.3</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>0.2 ± 0.2</t>
+          <t>0.9 ± 0.3</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -8124,37 +8124,37 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>24071.8 ± 235.1</t>
+          <t>40429.6 ± 201.4</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>13977.6 ± 129.7</t>
+          <t>23497.4 ± 138.6</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>38.0 ± 3.9</t>
+          <t>60.6 ± 2.4</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2.4 ± 0.5</t>
+          <t>3.7 ± 0.6</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>14.0 ± 1.8</t>
+          <t>21.5 ± 1.5</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>21.4 ± 1.9</t>
+          <t>34.5 ± 2.3</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>0.2 ± 0.2</t>
+          <t>0.8 ± 0.2</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -8179,37 +8179,37 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>23827.4 ± 235.7</t>
+          <t>40040.8 ± 199.0</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>13811.0 ± 131.9</t>
+          <t>23241.8 ± 136.8</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>37.8 ± 3.3</t>
+          <t>59.4 ± 2.3</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2.2 ± 0.6</t>
+          <t>3.6 ± 0.6</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>14.4 ± 1.7</t>
+          <t>21.0 ± 1.6</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>21.0 ± 1.4</t>
+          <t>34.0 ± 2.2</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>0.2 ± 0.2</t>
+          <t>0.8 ± 0.2</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -8234,37 +8234,37 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>23591.6 ± 233.5</t>
+          <t>39662.7 ± 199.3</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>13650.8 ± 131.3</t>
+          <t>22979.8 ± 134.9</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>37.8 ± 3.6</t>
+          <t>58.3 ± 2.4</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2.2 ± 0.6</t>
+          <t>3.6 ± 0.6</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>14.4 ± 1.9</t>
+          <t>20.6 ± 1.7</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>21.0 ± 1.5</t>
+          <t>33.3 ± 2.1</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>0.2 ± 0.2</t>
+          <t>0.8 ± 0.2</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -8289,37 +8289,37 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>23377.8 ± 231.8</t>
+          <t>39268.8 ± 201.0</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>13504.8 ± 137.0</t>
+          <t>22720.6 ± 137.6</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>37.6 ± 3.5</t>
+          <t>57.1 ± 2.4</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2.2 ± 0.6</t>
+          <t>3.5 ± 0.6</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>14.6 ± 1.7</t>
+          <t>20.3 ± 1.8</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>20.6 ± 1.6</t>
+          <t>32.6 ± 2.1</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>0.2 ± 0.2</t>
+          <t>0.8 ± 0.2</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -8344,37 +8344,37 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>23133.6 ± 241.1</t>
+          <t>38861.3 ± 201.8</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>13358.0 ± 137.2</t>
+          <t>22464.0 ± 138.1</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>37.6 ± 3.2</t>
+          <t>57.0 ± 2.3</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2.2 ± 0.6</t>
+          <t>3.4 ± 0.6</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>14.8 ± 1.6</t>
+          <t>20.1 ± 1.8</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20.6 ± 1.3</t>
+          <t>32.8 ± 2.2</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>0.0 ± 0.0</t>
+          <t>0.8 ± 0.2</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -8399,37 +8399,37 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>22890.0 ± 236.3</t>
+          <t>38449.2 ± 198.7</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>13201.6 ± 134.0</t>
+          <t>22192.0 ± 138.2</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>37.0 ± 3.1</t>
+          <t>56.2 ± 2.4</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2.0 ± 0.6</t>
+          <t>3.2 ± 0.5</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>14.4 ± 1.5</t>
+          <t>20.1 ± 1.8</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20.6 ± 1.4</t>
+          <t>32.2 ± 1.9</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>0.0 ± 0.0</t>
+          <t>0.7 ± 0.2</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -8454,37 +8454,37 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>22627.6 ± 223.4</t>
+          <t>38020.0 ± 198.9</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>13035.8 ± 127.7</t>
+          <t>21924.0 ± 136.5</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>36.8 ± 2.9</t>
+          <t>55.7 ± 2.5</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2.0 ± 0.6</t>
+          <t>3.4 ± 0.6</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>14.0 ± 1.5</t>
+          <t>19.8 ± 1.9</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>20.8 ± 1.2</t>
+          <t>31.9 ± 2.0</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>0.0 ± 0.0</t>
+          <t>0.7 ± 0.2</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -8509,37 +8509,37 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>22362.8 ± 224.2</t>
+          <t>37594.4 ± 195.3</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>12873.4 ± 128.0</t>
+          <t>21662.4 ± 134.7</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>35.6 ± 3.0</t>
+          <t>54.8 ± 2.4</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>1.8 ± 0.5</t>
+          <t>3.3 ± 0.6</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>13.2 ± 1.6</t>
+          <t>19.6 ± 1.8</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>20.6 ± 1.2</t>
+          <t>31.2 ± 1.8</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>0.0 ± 0.0</t>
+          <t>0.7 ± 0.2</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -8564,37 +8564,37 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>22133.8 ± 216.7</t>
+          <t>37184.8 ± 201.3</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>12719.4 ± 129.6</t>
+          <t>21420.1 ± 136.9</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>36.4 ± 2.9</t>
+          <t>54.0 ± 2.6</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2.0 ± 0.4</t>
+          <t>3.4 ± 0.6</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>13.0 ± 1.6</t>
+          <t>19.1 ± 1.8</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>21.4 ± 1.0</t>
+          <t>30.8 ± 1.9</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>0.0 ± 0.0</t>
+          <t>0.7 ± 0.2</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -8619,37 +8619,37 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>21863.2 ± 216.1</t>
+          <t>36725.6 ± 202.2</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>12560.8 ± 128.3</t>
+          <t>21156.3 ± 138.5</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>35.6 ± 3.1</t>
+          <t>53.3 ± 2.8</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2.0 ± 0.4</t>
+          <t>3.4 ± 0.6</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>13.0 ± 1.9</t>
+          <t>19.2 ± 1.7</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>20.6 ± 1.0</t>
+          <t>30.0 ± 1.9</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>0.0 ± 0.0</t>
+          <t>0.8 ± 0.3</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -8674,37 +8674,37 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>21610.2 ± 217.3</t>
+          <t>36287.9 ± 204.7</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>12420.0 ± 128.1</t>
+          <t>20904.3 ± 141.6</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>34.8 ± 3.1</t>
+          <t>52.1 ± 2.9</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2.0 ± 0.4</t>
+          <t>3.2 ± 0.6</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>12.6 ± 1.9</t>
+          <t>18.9 ± 1.6</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>20.2 ± 1.1</t>
+          <t>29.3 ± 1.9</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>0.0 ± 0.0</t>
+          <t>0.8 ± 0.3</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -8729,37 +8729,37 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>21366.0 ± 215.0</t>
+          <t>35849.4 ± 203.0</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>12287.4 ± 131.0</t>
+          <t>20660.3 ± 142.4</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>34.6 ± 2.9</t>
+          <t>52.4 ± 2.6</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2.0 ± 0.4</t>
+          <t>3.2 ± 0.6</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>13.0 ± 1.8</t>
+          <t>18.6 ± 1.7</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>19.6 ± 1.1</t>
+          <t>29.9 ± 1.8</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>0.0 ± 0.0</t>
+          <t>0.8 ± 0.3</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -8784,37 +8784,37 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>21095.4 ± 209.1</t>
+          <t>35443.0 ± 202.0</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>12126.4 ± 121.9</t>
+          <t>20427.8 ± 143.7</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>34.0 ± 2.6</t>
+          <t>51.4 ± 2.8</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2.0 ± 0.4</t>
+          <t>3.1 ± 0.6</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>12.6 ± 1.7</t>
+          <t>18.2 ± 1.6</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>19.4 ± 0.9</t>
+          <t>29.2 ± 2.0</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>0.0 ± 0.0</t>
+          <t>0.8 ± 0.3</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -8839,37 +8839,37 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>20830.6 ± 208.4</t>
+          <t>35024.8 ± 199.9</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>11983.0 ± 127.1</t>
+          <t>20193.2 ± 141.7</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>33.8 ± 2.3</t>
+          <t>49.9 ± 2.6</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2.0 ± 0.4</t>
+          <t>3.1 ± 0.6</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>13.0 ± 1.6</t>
+          <t>17.8 ± 1.5</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>18.8 ± 0.8</t>
+          <t>28.2 ± 2.1</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>0.0 ± 0.0</t>
+          <t>0.8 ± 0.3</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -8894,37 +8894,37 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>20567.0 ± 204.2</t>
+          <t>34616.4 ± 200.0</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>11842.2 ± 123.7</t>
+          <t>19967.8 ± 141.7</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>33.2 ± 2.0</t>
+          <t>49.6 ± 2.6</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>1.4 ± 0.3</t>
+          <t>3.0 ± 0.6</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>12.6 ± 1.5</t>
+          <t>17.9 ± 1.5</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>19.2 ± 0.7</t>
+          <t>27.9 ± 2.1</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>0.0 ± 0.0</t>
+          <t>0.8 ± 0.3</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -8949,37 +8949,37 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>20343.4 ± 214.8</t>
+          <t>34226.2 ± 196.8</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>11711.2 ± 127.2</t>
+          <t>19747.4 ± 137.0</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>33.0 ± 1.7</t>
+          <t>48.8 ± 2.4</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>1.2 ± 0.3</t>
+          <t>3.0 ± 0.6</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>12.6 ± 1.4</t>
+          <t>17.6 ± 1.5</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>19.2 ± 0.4</t>
+          <t>27.5 ± 2.0</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>0.0 ± 0.0</t>
+          <t>0.8 ± 0.2</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -9004,37 +9004,37 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>20116.2 ± 217.4</t>
+          <t>33839.4 ± 195.0</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>11589.8 ± 132.1</t>
+          <t>19532.8 ± 133.1</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>33.0 ± 1.9</t>
+          <t>48.3 ± 2.4</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>1.2 ± 0.3</t>
+          <t>3.0 ± 0.6</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>12.8 ± 1.6</t>
+          <t>17.1 ± 1.4</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>19.0 ± 0.3</t>
+          <t>27.4 ± 2.0</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>0.0 ± 0.0</t>
+          <t>0.8 ± 0.2</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -9059,37 +9059,37 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>19889.0 ± 216.4</t>
+          <t>33441.1 ± 193.4</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>11459.8 ± 144.5</t>
+          <t>19320.2 ± 133.0</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>33.0 ± 2.2</t>
+          <t>48.2 ± 2.2</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>1.2 ± 0.3</t>
+          <t>3.2 ± 0.6</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>12.8 ± 1.6</t>
+          <t>17.0 ± 1.3</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>19.0 ± 0.5</t>
+          <t>27.2 ± 2.0</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>0.0 ± 0.0</t>
+          <t>0.8 ± 0.2</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -9114,37 +9114,37 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>19660.6 ± 212.0</t>
+          <t>33062.7 ± 192.8</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>11325.8 ± 143.3</t>
+          <t>19108.5 ± 132.2</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>32.4 ± 1.9</t>
+          <t>47.6 ± 2.1</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>1.0 ± 0.3</t>
+          <t>3.2 ± 0.6</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>12.6 ± 1.5</t>
+          <t>16.8 ± 1.4</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>18.8 ± 0.5</t>
+          <t>26.9 ± 1.9</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>0.0 ± 0.0</t>
+          <t>0.8 ± 0.3</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -9169,37 +9169,37 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>19422.8 ± 211.3</t>
+          <t>32690.5 ± 189.3</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>11205.4 ± 148.5</t>
+          <t>18908.8 ± 130.1</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>31.2 ± 2.1</t>
+          <t>47.1 ± 1.9</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>1.0 ± 0.3</t>
+          <t>3.4 ± 0.7</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>12.0 ± 1.5</t>
+          <t>16.6 ± 1.3</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>18.2 ± 0.8</t>
+          <t>26.4 ± 1.8</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>0.0 ± 0.0</t>
+          <t>0.8 ± 0.3</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -9224,37 +9224,37 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>19192.0 ± 212.4</t>
+          <t>32317.0 ± 191.9</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>11078.8 ± 144.9</t>
+          <t>18709.3 ± 130.9</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>30.0 ± 1.8</t>
+          <t>45.8 ± 2.0</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>1.0 ± 0.3</t>
+          <t>3.0 ± 0.7</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>11.8 ± 1.4</t>
+          <t>15.9 ± 1.3</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>17.2 ± 0.9</t>
+          <t>25.9 ± 1.7</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>0.0 ± 0.0</t>
+          <t>0.8 ± 0.3</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -9279,37 +9279,37 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>18990.8 ± 218.6</t>
+          <t>31952.3 ± 187.1</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>10972.2 ± 148.2</t>
+          <t>18510.3 ± 128.8</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>30.2 ± 1.9</t>
+          <t>45.7 ± 2.0</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
+          <t>3.0 ± 0.7</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>15.9 ± 1.3</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>25.9 ± 1.8</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
           <t>0.8 ± 0.3</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>12.0 ± 1.5</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>17.4 ± 1.2</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>0.0 ± 0.0</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -9334,37 +9334,37 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>18792.4 ± 212.3</t>
+          <t>31612.6 ± 179.3</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>10859.6 ± 142.8</t>
+          <t>18313.5 ± 124.8</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>29.6 ± 1.7</t>
+          <t>45.0 ± 2.1</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
+          <t>3.1 ± 0.7</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>15.7 ± 1.3</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>25.4 ± 1.8</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
           <t>0.8 ± 0.3</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>11.8 ± 1.6</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>17.0 ± 1.2</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>0.0 ± 0.0</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -9389,37 +9389,37 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>18581.0 ± 211.2</t>
+          <t>31257.7 ± 175.3</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>10726.6 ± 139.0</t>
+          <t>18115.3 ± 126.3</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>29.8 ± 1.5</t>
+          <t>44.0 ± 2.1</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
+          <t>3.2 ± 0.7</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>15.0 ± 1.3</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>25.1 ± 1.8</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
           <t>0.8 ± 0.3</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>12.0 ± 1.6</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>17.0 ± 1.1</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>0.0 ± 0.0</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -9444,37 +9444,37 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>18377.0 ± 209.1</t>
+          <t>30909.0 ± 177.6</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>10618.2 ± 139.8</t>
+          <t>17912.3 ± 126.1</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>29.6 ± 1.7</t>
+          <t>43.5 ± 2.2</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>1.0 ± 0.3</t>
+          <t>3.1 ± 0.7</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>11.8 ± 1.5</t>
+          <t>14.4 ± 1.3</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>16.8 ± 1.1</t>
+          <t>25.2 ± 1.8</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>0.0 ± 0.0</t>
+          <t>0.7 ± 0.3</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -9499,37 +9499,37 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>18191.6 ± 206.4</t>
+          <t>30574.2 ± 177.7</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>10513.0 ± 143.6</t>
+          <t>17713.8 ± 122.5</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>28.8 ± 1.4</t>
+          <t>43.1 ± 2.2</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>0.8 ± 0.3</t>
+          <t>3.0 ± 0.7</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>11.6 ± 1.4</t>
+          <t>14.2 ± 1.4</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>16.4 ± 1.2</t>
+          <t>25.1 ± 1.9</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>0.0 ± 0.0</t>
+          <t>0.7 ± 0.3</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -9554,37 +9554,37 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>17984.8 ± 206.9</t>
+          <t>30251.2 ± 178.8</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>10392.6 ± 144.5</t>
+          <t>17516.1 ± 122.5</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>28.8 ± 1.3</t>
+          <t>42.8 ± 2.0</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>0.8 ± 0.3</t>
+          <t>3.0 ± 0.7</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>11.4 ± 1.3</t>
+          <t>13.8 ± 1.4</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>16.6 ± 1.1</t>
+          <t>25.4 ± 1.7</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>0.0 ± 0.0</t>
+          <t>0.7 ± 0.3</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -9609,37 +9609,37 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>17789.6 ± 208.9</t>
+          <t>29932.6 ± 176.9</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>10292.4 ± 145.0</t>
+          <t>17334.9 ± 121.4</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>28.0 ± 1.2</t>
+          <t>42.5 ± 2.1</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>0.8 ± 0.3</t>
+          <t>3.0 ± 0.7</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>10.8 ± 1.2</t>
+          <t>13.9 ± 1.4</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>16.4 ± 1.0</t>
+          <t>25.0 ± 1.8</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>0.0 ± 0.0</t>
+          <t>0.6 ± 0.2</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -9664,37 +9664,37 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>17624.4 ± 214.4</t>
+          <t>29627.3 ± 176.8</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>10181.2 ± 150.2</t>
+          <t>17147.3 ± 121.0</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>28.0 ± 1.3</t>
+          <t>41.9 ± 2.2</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>0.8 ± 0.3</t>
+          <t>3.0 ± 0.7</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>10.8 ± 1.4</t>
+          <t>13.8 ± 1.4</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>16.4 ± 1.1</t>
+          <t>24.5 ± 1.7</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>0.0 ± 0.0</t>
+          <t>0.7 ± 0.2</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -9719,37 +9719,37 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>17421.0 ± 212.1</t>
+          <t>29318.3 ± 180.4</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>10056.8 ± 144.5</t>
+          <t>16960.2 ± 120.4</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>25.6 ± 1.2</t>
+          <t>42.0 ± 2.1</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>0.8 ± 0.3</t>
+          <t>2.9 ± 0.7</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>10.0 ± 1.4</t>
+          <t>14.0 ± 1.5</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>14.8 ± 0.9</t>
+          <t>24.4 ± 1.6</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>0.0 ± 0.0</t>
+          <t>0.6 ± 0.2</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -9774,37 +9774,37 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>17214.8 ± 215.7</t>
+          <t>29007.6 ± 178.6</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>9936.4 ± 144.7</t>
+          <t>16773.1 ± 123.3</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>25.8 ± 1.2</t>
+          <t>41.5 ± 2.1</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>0.8 ± 0.3</t>
+          <t>2.9 ± 0.8</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>10.4 ± 1.5</t>
+          <t>13.8 ± 1.6</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>14.6 ± 0.7</t>
+          <t>24.2 ± 1.5</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>0.0 ± 0.0</t>
+          <t>0.6 ± 0.2</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -9829,37 +9829,37 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>17031.2 ± 217.9</t>
+          <t>28695.5 ± 175.5</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>9825.2 ± 147.1</t>
+          <t>16583.9 ± 126.4</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>26.0 ± 1.5</t>
+          <t>41.2 ± 2.1</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>0.8 ± 0.3</t>
+          <t>2.8 ± 0.8</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>10.2 ± 1.3</t>
+          <t>13.8 ± 1.5</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>15.0 ± 0.7</t>
+          <t>24.2 ± 1.5</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>0.0 ± 0.0</t>
+          <t>0.6 ± 0.2</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -9884,37 +9884,37 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>16839.8 ± 208.1</t>
+          <t>28394.0 ± 176.8</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>9705.0 ± 147.7</t>
+          <t>16401.0 ± 123.9</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>26.0 ± 1.5</t>
+          <t>41.4 ± 2.2</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>0.8 ± 0.3</t>
+          <t>2.7 ± 0.8</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>10.0 ± 1.3</t>
+          <t>13.9 ± 1.6</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>15.2 ± 0.7</t>
+          <t>24.2 ± 1.3</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>0.0 ± 0.0</t>
+          <t>0.5 ± 0.2</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -9939,37 +9939,37 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>16670.2 ± 205.2</t>
+          <t>28076.0 ± 180.4</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>9591.2 ± 150.7</t>
+          <t>16211.2 ± 126.4</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>25.6 ± 1.4</t>
+          <t>41.2 ± 1.9</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>0.8 ± 0.3</t>
+          <t>2.6 ± 0.7</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>9.8 ± 1.2</t>
+          <t>14.1 ± 1.6</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>15.0 ± 0.8</t>
+          <t>24.0 ± 1.3</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>0.0 ± 0.0</t>
+          <t>0.5 ± 0.2</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -9994,37 +9994,37 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>16487.8 ± 203.3</t>
+          <t>27755.8 ± 177.6</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>9495.8 ± 148.1</t>
+          <t>16024.1 ± 124.1</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>25.8 ± 1.5</t>
+          <t>40.6 ± 1.8</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>1.0 ± 0.3</t>
+          <t>2.6 ± 0.7</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>9.8 ± 1.2</t>
+          <t>13.8 ± 1.7</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>14.8 ± 0.9</t>
+          <t>23.9 ± 1.3</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>0.2 ± 0.2</t>
+          <t>0.5 ± 0.2</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -10049,37 +10049,37 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>16296.6 ± 201.5</t>
+          <t>27456.8 ± 174.6</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>9384.6 ± 151.1</t>
+          <t>15846.5 ± 124.1</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>26.0 ± 1.5</t>
+          <t>40.5 ± 1.5</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>1.0 ± 0.3</t>
+          <t>2.6 ± 0.7</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>9.6 ± 1.3</t>
+          <t>13.8 ± 1.6</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>15.2 ± 0.5</t>
+          <t>23.6 ± 1.3</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>0.2 ± 0.2</t>
+          <t>0.5 ± 0.2</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -10104,37 +10104,37 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>16125.4 ± 199.6</t>
+          <t>27155.0 ± 173.7</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>9283.2 ± 153.3</t>
+          <t>15666.2 ± 125.1</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>25.2 ± 1.6</t>
+          <t>40.0 ± 1.7</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>1.0 ± 0.3</t>
+          <t>2.6 ± 0.7</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>9.2 ± 1.3</t>
+          <t>13.6 ± 1.6</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>14.8 ± 0.7</t>
+          <t>23.4 ± 1.4</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>0.2 ± 0.2</t>
+          <t>0.5 ± 0.2</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
